--- a/DATA/MASTER/C10_MASTER/Preparacion_Machine_Learning/catalogo_conocimiento/catalogo_conocimiento_variables.xlsx
+++ b/DATA/MASTER/C10_MASTER/Preparacion_Machine_Learning/catalogo_conocimiento/catalogo_conocimiento_variables.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,6 +1330,106 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Anio</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Permite identificar tendencias temporales de largo plazo en las variables del sistema hídrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Representa la estacionalidad anual, fundamental para explicar la variabilidad climática e hidrológica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Anio</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Permite identificar tendencias temporales de largo plazo en las variables del sistema hídrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Representa la estacionalidad anual, fundamental para explicar la variabilidad climática e hidrológica.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DATA/MASTER/C10_MASTER/Preparacion_Machine_Learning/catalogo_conocimiento/catalogo_conocimiento_variables.xlsx
+++ b/DATA/MASTER/C10_MASTER/Preparacion_Machine_Learning/catalogo_conocimiento/catalogo_conocimiento_variables.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1322,109 +1322,9 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>Representa la estacionalidad anual, fundamental para explicar la variabilidad climática e hidrológica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Anio</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Permite identificar tendencias temporales de largo plazo en las variables del sistema hídrico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Representa la estacionalidad anual, fundamental para explicar la variabilidad climática e hidrológica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Anio</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Permite identificar tendencias temporales de largo plazo en las variables del sistema hídrico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>Representa la estacionalidad anual, fundamental para explicar la variabilidad climática e hidrológica.</t>
         </is>
